--- a/jpcore-r4/feature/swg2-dental/observations-summary.xlsx
+++ b/jpcore-r4/feature/swg2-dental/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="74">
   <si>
     <t>Profile</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>JP Core Observation DentalOral Tooth Existence Profile</t>
+  </si>
+  <si>
+    <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#LP89803-8, JP Core ObservationDentalCategory CodeSystem#DO-1-01</t>
   </si>
   <si>
     <t>jp-observation-dentaloral-toothtreatmentcondition</t>
@@ -480,7 +483,7 @@
         <v>27</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s" s="2">
         <v>14</v>
@@ -509,10 +512,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>21</v>
@@ -544,25 +547,25 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>17</v>
@@ -579,13 +582,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>14</v>
@@ -594,13 +597,13 @@
         <v>14</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>18</v>
@@ -614,13 +617,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s" s="2">
         <v>14</v>
@@ -629,13 +632,13 @@
         <v>14</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>18</v>
@@ -649,13 +652,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s" s="2">
         <v>14</v>
@@ -664,13 +667,13 @@
         <v>14</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>18</v>
@@ -684,22 +687,22 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F10" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>16</v>
@@ -719,10 +722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>14</v>
@@ -731,7 +734,7 @@
         <v>14</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>23</v>
@@ -740,7 +743,7 @@
         <v>24</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>18</v>
@@ -754,10 +757,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>14</v>
@@ -766,7 +769,7 @@
         <v>14</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>23</v>
@@ -775,7 +778,7 @@
         <v>24</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>18</v>
@@ -789,13 +792,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>14</v>
@@ -804,13 +807,13 @@
         <v>14</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>18</v>
@@ -824,13 +827,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>14</v>
@@ -839,7 +842,7 @@
         <v>14</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>16</v>

--- a/jpcore-r4/feature/swg2-dental/observations-summary.xlsx
+++ b/jpcore-r4/feature/swg2-dental/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="75">
   <si>
     <t>Profile</t>
   </si>
@@ -77,7 +77,7 @@
     <t>JP Core Observation DentalOral Missing Tooth Condition Profile</t>
   </si>
   <si>
-    <t>LOINC#LP89803-8</t>
+    <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#LP89803-8, JP Core ObservationDentalCategory CodeSystem#MissingToothCondition</t>
   </si>
   <si>
     <t>null#54570-7</t>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>JP Core Observation DentalOral Tooth Treatment Condition Profile</t>
+  </si>
+  <si>
+    <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#LP89803-8, JP Core ObservationDentalCategory CodeSystem#DO-1-02</t>
   </si>
   <si>
     <t>jp-observation-electrocardiogram</t>
@@ -518,7 +521,7 @@
         <v>30</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>14</v>
@@ -547,25 +550,25 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>17</v>
@@ -582,13 +585,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>14</v>
@@ -597,13 +600,13 @@
         <v>14</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>18</v>
@@ -617,13 +620,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s" s="2">
         <v>14</v>
@@ -632,13 +635,13 @@
         <v>14</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>18</v>
@@ -652,13 +655,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s" s="2">
         <v>14</v>
@@ -667,13 +670,13 @@
         <v>14</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>18</v>
@@ -687,22 +690,22 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F10" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>16</v>
@@ -722,10 +725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>14</v>
@@ -734,7 +737,7 @@
         <v>14</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>23</v>
@@ -743,7 +746,7 @@
         <v>24</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>18</v>
@@ -757,10 +760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>14</v>
@@ -769,7 +772,7 @@
         <v>14</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>23</v>
@@ -778,7 +781,7 @@
         <v>24</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>18</v>
@@ -792,13 +795,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>14</v>
@@ -807,13 +810,13 @@
         <v>14</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>18</v>
@@ -827,13 +830,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>14</v>
@@ -842,7 +845,7 @@
         <v>14</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>16</v>

--- a/jpcore-r4/feature/swg2-dental/observations-summary.xlsx
+++ b/jpcore-r4/feature/swg2-dental/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="74">
   <si>
     <t>Profile</t>
   </si>
@@ -119,13 +119,10 @@
     <t>null#procedure</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS (required)</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramExtraCategory_VS (example)</t>
   </si>
   <si>
     <t>null#11524-6</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramComponentCode_VS (preferred)</t>
   </si>
   <si>
     <t>dateTime, Period, Timing, instant</t>
@@ -565,10 +562,10 @@
         <v>36</v>
       </c>
       <c r="F6" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s" s="2">
         <v>37</v>
-      </c>
-      <c r="G6" t="s" s="2">
-        <v>38</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>17</v>
@@ -585,28 +582,28 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="B7" t="s" s="2">
+      <c r="C7" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="C7" t="s" s="2">
+      <c r="D7" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s" s="2">
         <v>41</v>
       </c>
-      <c r="D7" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E7" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s" s="2">
+      <c r="G7" t="s" s="2">
         <v>42</v>
       </c>
-      <c r="G7" t="s" s="2">
+      <c r="H7" t="s" s="2">
         <v>43</v>
-      </c>
-      <c r="H7" t="s" s="2">
-        <v>44</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>18</v>
@@ -620,28 +617,28 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="B8" t="s" s="2">
+      <c r="C8" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="C8" t="s" s="2">
+      <c r="D8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s" s="2">
         <v>47</v>
       </c>
-      <c r="D8" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F8" t="s" s="2">
+      <c r="G8" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="G8" t="s" s="2">
+      <c r="H8" t="s" s="2">
         <v>49</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>50</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>18</v>
@@ -655,28 +652,28 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="B9" t="s" s="2">
+      <c r="C9" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="C9" t="s" s="2">
+      <c r="D9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s" s="2">
         <v>53</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F9" t="s" s="2">
-        <v>54</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>18</v>
@@ -690,22 +687,22 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="B10" t="s" s="2">
+      <c r="C10" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="C10" t="s" s="2">
+      <c r="D10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s" s="2">
         <v>57</v>
       </c>
-      <c r="D10" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E10" t="s" s="2">
+      <c r="F10" t="s" s="2">
         <v>58</v>
-      </c>
-      <c r="F10" t="s" s="2">
-        <v>59</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>16</v>
@@ -725,19 +722,19 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="B11" t="s" s="2">
+      <c r="C11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s" s="2">
         <v>61</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s" s="2">
-        <v>62</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>23</v>
@@ -746,7 +743,7 @@
         <v>24</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>18</v>
@@ -760,19 +757,19 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="B12" t="s" s="2">
+      <c r="C12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s" s="2">
         <v>65</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E12" t="s" s="2">
-        <v>66</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>23</v>
@@ -781,7 +778,7 @@
         <v>24</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>18</v>
@@ -795,28 +792,28 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="B13" t="s" s="2">
+      <c r="C13" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="C13" t="s" s="2">
+      <c r="D13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F13" t="s" s="2">
         <v>69</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E13" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F13" t="s" s="2">
-        <v>70</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>18</v>
@@ -830,22 +827,22 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="B14" t="s" s="2">
+      <c r="C14" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="C14" t="s" s="2">
+      <c r="D14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F14" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E14" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F14" t="s" s="2">
-        <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>16</v>
